--- a/output/pdf_financials_xlsx/HEAL.xlsx
+++ b/output/pdf_financials_xlsx/HEAL.xlsx
@@ -907,7 +907,7 @@
         <v>0.224745</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.224745</v>
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="24">
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>8.032036</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>8.285869999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>8.249250999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.360099</v>
       </c>
     </row>
     <row r="93">
@@ -2400,10 +2400,10 @@
         <v>-1.224422</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.224745</v>
+        <v>-0.224745</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.224745</v>
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="100">
@@ -3644,7 +3644,11 @@
           <t>Reserves 9, 12</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4702,7 +4706,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4996,7 +5004,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>8.032036</v>
       </c>
@@ -6010,10 +6022,10 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.224745</v>
+        <v>-0.224745</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.224745</v>
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="82">

--- a/output/pdf_financials_xlsx/HEAL.xlsx
+++ b/output/pdf_financials_xlsx/HEAL.xlsx
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000576</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.465886</v>
+        <v>-2.466462</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.224422</v>
+        <v>-1.224424</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.224745</v>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.465886</v>
+        <v>-2.466462</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.224422</v>
+        <v>-1.224424</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.224745</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">

--- a/output/pdf_financials_xlsx/HEAL.xlsx
+++ b/output/pdf_financials_xlsx/HEAL.xlsx
@@ -516,10 +516,8 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -556,12 +554,10 @@
         <v>0.866467</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.584734</v>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.353078</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.293743</v>
       </c>
     </row>
     <row r="8">
@@ -579,10 +575,8 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -600,10 +594,8 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -619,12 +611,10 @@
         <v>0.866467</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.584734</v>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.353078</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.293743</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +653,8 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -684,10 +672,8 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -705,10 +691,8 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -726,10 +710,8 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -747,10 +729,8 @@
       <c r="D16" s="3" t="n">
         <v>0.224745</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="17">
@@ -768,10 +748,8 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -843,10 +821,8 @@
       <c r="D20" s="3" t="n">
         <v>0.224745</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="21">
@@ -864,10 +840,8 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -885,10 +859,8 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -988,10 +960,8 @@
       <c r="D27" s="3" t="n">
         <v>0.224745</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="28">
@@ -1009,10 +979,8 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1030,10 +998,8 @@
       <c r="D29" s="3" t="n">
         <v>0.224745</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-0.224745</v>
       </c>
     </row>
     <row r="30">
@@ -1078,10 +1044,8 @@
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3109,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6116,7 +6080,11 @@
           <t>Private placement 12 22,300,000 1,654,939 8,261</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -8232,28 +8200,30 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>immediately</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Accounting, legal and audit</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>0.08495999999999999</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.046569</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.038589</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002026</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>1e-06</v>
       </c>
     </row>
     <row r="143">
@@ -8264,29 +8234,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>5.    MARKETABLE SECURITIES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Amortization 7</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>2025, the Company recorded an unrealized loss on short-term investments of $105,110 (2024</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F143" s="5" t="n">
-        <v>0.002941</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.002311</v>
+        <v>0.144526</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -8302,32 +8270,30 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>b) Liquidity risk</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0.7797460000000001</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>0.469566</v>
+          <t>sufficient liquid funds to meet its liabilities when due, under both normal and stressed conditions, without incurring unacceptable losses or risking damage to the Company’s reputation. As of December</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.22977</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="145">
@@ -8338,32 +8304,30 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>0.222</v>
+          <t>Balance, December 31, 2025 and 2024 16,173</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.23014</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.056053</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>0.03988</v>
       </c>
     </row>
     <row r="146">
@@ -8374,32 +8338,30 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated Amortization</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n">
-        <v>0.311384</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>0.119636</v>
+          <t>Balance, December 31, 2023 16,076</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.092526</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04467</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>0.028594</v>
       </c>
     </row>
     <row r="147">
@@ -8410,30 +8372,34 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated Amortization</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Share-based payments 13</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Amortization 54</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F147" s="5" t="n">
-        <v>0.273375</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.032381</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002311</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>0.002257</v>
       </c>
     </row>
     <row r="148">
@@ -8444,32 +8410,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated Amortization</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Shareholder communications and investor relations</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>0.05525</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>0.033013</v>
+          <t>Balance, December 31, 2024 16,130</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.008961</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.046981</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>0.030851</v>
       </c>
     </row>
     <row r="149">
@@ -8480,32 +8444,34 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated Amortization</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Amortization 43</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0.036526</v>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>0.022252</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.023337</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00185</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>0.001807</v>
       </c>
     </row>
     <row r="150">
@@ -8516,28 +8482,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accumulated Amortization</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Research and development costs</t>
+          <t>Balance, December 31, 2025 16,173</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>0.115163</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>0.07115100000000001</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.048831</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>0.032658</v>
       </c>
     </row>
     <row r="151">
@@ -8548,32 +8516,30 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net Book Value</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Loss before Other Items</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="n">
-        <v>-1.937274</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>-1.260503</v>
+          <t>Net Book Value, December 31, 2024 43</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>-0.658515</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009072</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>0.009029000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8584,12 +8550,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net Book Value</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Royalty income</t>
+          <t>Net Book Value, December 31, 2025 -</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -8598,18 +8564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0.028346</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.007222</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>0.007222</v>
       </c>
     </row>
     <row r="153">
@@ -8620,12 +8584,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>8.    LOAN RECEIVABLE FROM JUST KUSH</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Recovery of loan from Just Kush 8</t>
+          <t>$40,000 for each extension to be added to its indebtedness to the Company. Just Kush requested two such extensions, and extension fees of $80,000 were added to the principal of the loan. At December</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -8634,16 +8598,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.007735</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.001357</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="154">
@@ -8654,12 +8618,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>9.    LOAN AGREEMENTS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Gain on sale of intellectual property 17</t>
+          <t>value of the financial liability was calculated at $245,359 using the present value approach, and the residual value of $4,641 was assigned to the equity component and is included in Reserves at December</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -8674,12 +8638,10 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.6348510000000001</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="155">
@@ -8690,12 +8652,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>warrant.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Loss on short-term investments 5</t>
+          <t>was recognized as additional management and consulting expenses of $26,260 and $131,519, respectively, on the statement (loss) income and comprehensive (loss) income for the year ended December</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -8710,12 +8672,10 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>-0.144526</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="156">
@@ -8726,15 +8686,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Directors in adherence to conflict-of-interest laws and regulations.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Fair value adjustments 10</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -8746,12 +8710,10 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.00168</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.123037</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="157">
@@ -8762,17 +8724,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Directors in adherence to conflict-of-interest laws and regulations.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Gain on foreign exchange</t>
+          <t>Management fees</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8786,12 +8748,10 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.008359999999999999</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.230041</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0.262743</v>
       </c>
     </row>
     <row r="158">
@@ -8802,12 +8762,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Directors in adherence to conflict-of-interest laws and regulations.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt 11</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -8821,13 +8781,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G158" s="5" t="n">
-        <v>0.381538</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0.192722</v>
       </c>
     </row>
     <row r="159">
@@ -8838,34 +8798,30 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>a)  Issued share capital</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Net Income (Loss) and Comprehensive Income (Loss) for the Year</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>During the year ended December</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n">
-        <v>-1.224422</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.224745</v>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="160">
@@ -8876,34 +8832,30 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>fair value of $5,490 (see note 12b)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Income (Loss) and Comprehensive Income (Loss) Per Share, Basic</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>During the year ended December</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F160" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="161">
@@ -8914,34 +8866,30 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>b)  Warrants</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Income (Loss) and Comprehensive Income (Loss) Per Share, Diluted</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>During the year ended December</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F161" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="162">
@@ -8952,34 +8900,30 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares Outstanding</t>
+          <t>notes 10 and 12a.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>- Basic</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>$0.046. Accordingly, $2,771 was recognized in Reserves during the year ended December</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F162" s="5" t="n">
-        <v>14.676331</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>15.286045</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="163">
@@ -8990,34 +8934,30 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares Outstanding</t>
+          <t>under the residual value method.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>- Diluted</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>The weighted average issue date fair value of each option was $0.042. Accordingly, $5,490 was recognized in Reserves during the year ended December</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>14.676331</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>16.113777</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="164">
@@ -9033,24 +8973,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Amortization 6</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Accounting, legal and audit</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" s="5" t="n">
-        <v>0.003792</v>
+        <v>0.08495999999999999</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.002941</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.046569</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.038589</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -9071,20 +9005,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share-based payments 10</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>0.328453</v>
+          <t>Amortization 7</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0.273375</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002941</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.002311</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -9105,22 +9043,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Royalty income 11</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0.7797460000000001</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>0.028346</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.469566</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.22977</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -9141,22 +9079,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Recovery of loan from Just Kush 7</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>0.222</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.007735</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.222</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.23014</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -9177,22 +9115,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Write-off of payables (receivables)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="n">
-        <v>-0.001608</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.311384</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>0.119636</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.092526</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -9213,22 +9151,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Accretion of loan receivable from Just Kush 7</t>
+          <t>Share-based payments 13</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>0.229505</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>0.273375</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.032381</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -9249,22 +9185,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Recovery of accounts payable</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Shareholder communications and investor relations</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
-        <v>0.007691</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05525</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.033013</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.008961</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -9285,24 +9221,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0.000576</v>
+        <v>0.036526</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022252</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.023337</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -9323,22 +9257,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Impairment of loan receivable 7</t>
+          <t>Research and development costs</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" s="5" t="n">
-        <v>-0.764776</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.115163</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.07115100000000001</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.0005</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -9359,24 +9289,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year</t>
+          <t>Loss before Other Items</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>-2.465886</v>
+        <v>-1.937274</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>-1.224422</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.260503</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-0.658515</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -9397,19 +9325,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Loss and Comprehensive Loss Per Share, Basic and Diluted</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>-2e-08</v>
+          <t>Royalty income</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.028346</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -9430,27 +9356,837 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Recovery of loan from Just Kush 8</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>0.007735</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Gain on sale of intellectual property 17</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.6348510000000001</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Loss on short-term investments 5</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>-0.144526</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Fair value adjustments 10</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Gain on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.008359999999999999</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Gain on settlement of debt 11</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.381538</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Net Income (Loss) and Comprehensive Income (Loss) for the Year</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>-1.224422</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.224745</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Income (Loss) and Comprehensive Income (Loss) Per Share, Basic</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Income (Loss) and Comprehensive Income (Loss) Per Share, Diluted</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
           <t>Weighted Average Number of Common Shares Outstanding</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>- Basic</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>14.676331</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>15.286045</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>- Diluted</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>14.676331</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>16.113777</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Amortization 6</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>0.003792</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.002941</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Share-based payments 10</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>0.328453</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>0.273375</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Royalty income 11</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.028346</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Recovery of loan from Just Kush 7</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.007735</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Write-off of payables (receivables)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>-0.001608</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Accretion of loan receivable from Just Kush 7</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" s="5" t="n">
+        <v>0.229505</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Recovery of accounts payable</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
+        <v>0.007691</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>0.000576</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Impairment of loan receivable 7</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>-0.764776</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n">
+        <v>-2.465886</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>-1.224422</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Loss and Comprehensive Loss Per Share, Basic and Diluted</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>- Basic and Diluted</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" s="5" t="n">
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="5" t="n">
         <v>136.564707</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F197" s="5" t="n">
         <v>146.763312</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
